--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/SURENDRANAGAR.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/SURENDRANAGAR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026-27\ICS\2.0   PLANNING 2026-27\Kharif 2026-27\2.0\2.0 planning 2026-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Grv\Grv\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\02_GJ_WP_2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE41550-C5E4-4B52-8556-4E7E936B5028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F3FCB4-B229-4D79-8BCB-9B9C5A4D9998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="central 2.0" sheetId="1" r:id="rId1"/>
@@ -31,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="78">
   <si>
     <t xml:space="preserve">                               GUJARAT                                              STATEMENT NO. 4                                                  CENTRAL                                                                                      </t>
   </si>
@@ -271,6 +269,9 @@
   </si>
   <si>
     <t xml:space="preserve">                               GUJARAT                                              STATEMENT NO. 4                                                 STATE                                                                                   </t>
+  </si>
+  <si>
+    <t>ZZZ</t>
   </si>
 </sst>
 </file>
@@ -515,10 +516,26 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -539,25 +556,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -839,50 +840,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-    </row>
-    <row r="2" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+    </row>
+    <row r="2" spans="1:14" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-    </row>
-    <row r="3" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+    </row>
+    <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>2</v>
       </c>
@@ -900,68 +901,68 @@
       <c r="M3" s="15"/>
       <c r="N3" s="15"/>
     </row>
-    <row r="4" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="20" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="20">
         <v>10</v>
       </c>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22">
+      <c r="E4" s="20"/>
+      <c r="F4" s="20">
         <v>14</v>
       </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22">
+      <c r="G4" s="20"/>
+      <c r="H4" s="20">
         <v>12</v>
       </c>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22">
+      <c r="I4" s="20"/>
+      <c r="J4" s="20">
         <v>18</v>
       </c>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22">
+      <c r="K4" s="20"/>
+      <c r="L4" s="20">
         <v>10</v>
       </c>
-      <c r="M4" s="22"/>
+      <c r="M4" s="20"/>
       <c r="N4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="26" t="s">
+    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26" t="s">
+      <c r="E5" s="19"/>
+      <c r="F5" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26" t="s">
+      <c r="G5" s="19"/>
+      <c r="H5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26" t="s">
+      <c r="I5" s="19"/>
+      <c r="J5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26" t="s">
+      <c r="K5" s="19"/>
+      <c r="L5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="26"/>
+      <c r="M5" s="19"/>
       <c r="N5" s="1">
         <f>D4+F4+H4+J4+L4</f>
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1003,7 +1004,7 @@
       </c>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
@@ -1029,7 +1030,7 @@
       <c r="M7" s="9"/>
       <c r="N7" s="10"/>
     </row>
-    <row r="8" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>19</v>
       </c>
@@ -1063,7 +1064,7 @@
       <c r="M8" s="9"/>
       <c r="N8" s="10"/>
     </row>
-    <row r="9" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>19</v>
       </c>
@@ -1089,7 +1090,7 @@
       <c r="M9" s="9"/>
       <c r="N9" s="10"/>
     </row>
-    <row r="10" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>22</v>
       </c>
@@ -1115,7 +1116,7 @@
       </c>
       <c r="N10" s="10"/>
     </row>
-    <row r="11" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>24</v>
       </c>
@@ -1141,7 +1142,7 @@
       <c r="M11" s="6"/>
       <c r="N11" s="10"/>
     </row>
-    <row r="12" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>24</v>
       </c>
@@ -1167,7 +1168,7 @@
       <c r="M12" s="6"/>
       <c r="N12" s="10"/>
     </row>
-    <row r="13" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>24</v>
       </c>
@@ -1193,7 +1194,7 @@
       <c r="M13" s="6"/>
       <c r="N13" s="10"/>
     </row>
-    <row r="14" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>28</v>
       </c>
@@ -1227,7 +1228,7 @@
       </c>
       <c r="N14" s="10"/>
     </row>
-    <row r="15" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>28</v>
       </c>
@@ -1261,7 +1262,7 @@
       <c r="M15" s="6"/>
       <c r="N15" s="10"/>
     </row>
-    <row r="16" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>31</v>
       </c>
@@ -1295,7 +1296,7 @@
       </c>
       <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>31</v>
       </c>
@@ -1325,7 +1326,7 @@
       </c>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>34</v>
       </c>
@@ -1355,7 +1356,7 @@
       <c r="M18" s="6"/>
       <c r="N18" s="10"/>
     </row>
-    <row r="19" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>34</v>
       </c>
@@ -1389,7 +1390,7 @@
       <c r="M19" s="6"/>
       <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>37</v>
       </c>
@@ -1419,7 +1420,7 @@
       <c r="M20" s="6"/>
       <c r="N20" s="10"/>
     </row>
-    <row r="21" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
@@ -1449,7 +1450,7 @@
       </c>
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>41</v>
       </c>
@@ -1475,12 +1476,12 @@
       <c r="M22" s="9"/>
       <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
+    <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.3">
+      <c r="A23" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
       <c r="D23" s="4">
         <f>SUM(D7:D22)</f>
         <v>10</v>
@@ -1511,7 +1512,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>13</v>
       </c>
@@ -1529,7 +1530,7 @@
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
     </row>
-    <row r="25" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>28</v>
       </c>
@@ -1555,7 +1556,7 @@
       <c r="M25" s="4"/>
       <c r="N25" s="10"/>
     </row>
-    <row r="26" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>34</v>
       </c>
@@ -1581,12 +1582,12 @@
       <c r="M26" s="4"/>
       <c r="N26" s="10"/>
     </row>
-    <row r="27" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="23" t="s">
+    <row r="27" spans="1:14" ht="18" x14ac:dyDescent="0.3">
+      <c r="A27" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="25"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="18"/>
       <c r="D27" s="4">
         <f>SUM(D25:D26)</f>
         <v>0</v>
@@ -1616,12 +1617,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="23" t="s">
+    <row r="28" spans="1:14" ht="18" x14ac:dyDescent="0.3">
+      <c r="A28" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="25"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="18"/>
       <c r="D28" s="4">
         <f>+D23+D27</f>
         <v>10</v>
@@ -1654,15 +1655,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:N24"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
@@ -1673,6 +1665,15 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="L4:M4"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:N24"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1681,49 +1682,49 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-    </row>
-    <row r="2" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+    </row>
+    <row r="2" spans="1:14" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-    </row>
-    <row r="3" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+    </row>
+    <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>2</v>
       </c>
@@ -1741,68 +1742,68 @@
       <c r="M3" s="15"/>
       <c r="N3" s="15"/>
     </row>
-    <row r="4" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="20" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="28">
         <v>6</v>
       </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27">
+      <c r="E4" s="28"/>
+      <c r="F4" s="28">
         <v>10</v>
       </c>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27">
+      <c r="G4" s="28"/>
+      <c r="H4" s="28">
         <v>8</v>
       </c>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27">
+      <c r="I4" s="28"/>
+      <c r="J4" s="28">
         <v>10</v>
       </c>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27">
+      <c r="K4" s="28"/>
+      <c r="L4" s="28">
         <v>6</v>
       </c>
-      <c r="M4" s="27"/>
+      <c r="M4" s="28"/>
       <c r="N4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="26" t="s">
+    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26" t="s">
+      <c r="E5" s="19"/>
+      <c r="F5" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26" t="s">
+      <c r="G5" s="19"/>
+      <c r="H5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26" t="s">
+      <c r="I5" s="19"/>
+      <c r="J5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26" t="s">
+      <c r="K5" s="19"/>
+      <c r="L5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="26"/>
+      <c r="M5" s="19"/>
       <c r="N5" s="1">
         <f>D4+F4+H4+J4+L4</f>
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1844,11 +1845,13 @@
       </c>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="7"/>
+      <c r="B7" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="C7" s="7" t="s">
         <v>49</v>
       </c>
@@ -1868,7 +1871,7 @@
       <c r="M7" s="11"/>
       <c r="N7" s="10"/>
     </row>
-    <row r="8" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>22</v>
       </c>
@@ -1894,11 +1897,11 @@
       </c>
       <c r="N8" s="10"/>
     </row>
-    <row r="9" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="14" t="s">
         <v>75</v>
       </c>
       <c r="C9" s="7" t="s">
@@ -1920,11 +1923,11 @@
       <c r="M9" s="4"/>
       <c r="N9" s="10"/>
     </row>
-    <row r="10" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="14" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="7" t="s">
@@ -1946,7 +1949,7 @@
       <c r="M10" s="4"/>
       <c r="N10" s="10"/>
     </row>
-    <row r="11" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>28</v>
       </c>
@@ -1980,7 +1983,7 @@
       <c r="M11" s="4"/>
       <c r="N11" s="10"/>
     </row>
-    <row r="12" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>28</v>
       </c>
@@ -2010,7 +2013,7 @@
       <c r="M12" s="4"/>
       <c r="N12" s="10"/>
     </row>
-    <row r="13" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>34</v>
       </c>
@@ -2036,7 +2039,7 @@
       <c r="M13" s="4"/>
       <c r="N13" s="10"/>
     </row>
-    <row r="14" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>34</v>
       </c>
@@ -2062,7 +2065,7 @@
       </c>
       <c r="N14" s="10"/>
     </row>
-    <row r="15" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>37</v>
       </c>
@@ -2092,7 +2095,7 @@
       </c>
       <c r="N15" s="10"/>
     </row>
-    <row r="16" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>37</v>
       </c>
@@ -2118,7 +2121,7 @@
       <c r="M16" s="11"/>
       <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>40</v>
       </c>
@@ -2148,7 +2151,7 @@
       <c r="M17" s="11"/>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>43</v>
       </c>
@@ -2174,12 +2177,12 @@
       <c r="M18" s="11"/>
       <c r="N18" s="10"/>
     </row>
-    <row r="19" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="s">
+    <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.3">
+      <c r="A19" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
       <c r="D19" s="4">
         <f>SUM(D7:D18)</f>
         <v>6</v>
@@ -2210,7 +2213,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>13</v>
       </c>
@@ -2228,7 +2231,7 @@
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
     </row>
-    <row r="21" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>19</v>
       </c>
@@ -2254,7 +2257,7 @@
       <c r="M21" s="12"/>
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>34</v>
       </c>
@@ -2280,7 +2283,7 @@
       <c r="M22" s="12"/>
       <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>34</v>
       </c>
@@ -2306,12 +2309,12 @@
       <c r="M23" s="12"/>
       <c r="N23" s="10"/>
     </row>
-    <row r="24" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="23" t="s">
+    <row r="24" spans="1:14" ht="18" x14ac:dyDescent="0.3">
+      <c r="A24" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="25"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="18"/>
       <c r="D24" s="4">
         <f>SUM(D21:D23)</f>
         <v>0</v>
@@ -2341,12 +2344,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="23" t="s">
+    <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.3">
+      <c r="A25" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="24"/>
-      <c r="C25" s="25"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="18"/>
       <c r="D25" s="4">
         <f>+D19+D24</f>
         <v>6</v>
@@ -2378,17 +2381,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:N20" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="19">
-    <mergeCell ref="A20:N20"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
@@ -2399,6 +2392,15 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="L4:M4"/>
+    <mergeCell ref="A20:N20"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="A19:C19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
